--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484292_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484292_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0819</v>
+        <v>3.3276</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8411</v>
+        <v>1.2579</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7592</v>
+        <v>2.0697</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9344</v>
+        <v>-2.1639</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0202</v>
+        <v>-2.9338</v>
       </c>
       <c r="I2" t="n">
-        <v>2.9141</v>
+        <v>0.7698</v>
       </c>
       <c r="J2" t="n">
-        <v>4.522</v>
+        <v>-0.6409</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7982</v>
+        <v>-2.4905</v>
       </c>
       <c r="L2" t="n">
-        <v>3.7238</v>
+        <v>1.8496</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.5876</v>
+        <v>-1.523</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7779</v>
+        <v>-0.4433</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8097</v>
+        <v>-1.0797</v>
       </c>
       <c r="P2" t="n">
-        <v>0.586</v>
+        <v>2.1488</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5627</v>
+        <v>3.1255</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4385</v>
+        <v>-0.6452</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0772</v>
+        <v>-0.4483</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5157</v>
+        <v>-0.1969</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>3.988</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2186</v>
+        <v>3.3238</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2675</v>
+        <v>3.2398</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3885</v>
+        <v>4.6994</v>
       </c>
       <c r="F3" t="n">
-        <v>1.879</v>
+        <v>-1.4596</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.1639</v>
+        <v>2.9344</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.9338</v>
+        <v>0.0202</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7698</v>
+        <v>2.9141</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.6409</v>
+        <v>4.522</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.4905</v>
+        <v>0.7982</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8496</v>
+        <v>3.7238</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.523</v>
+        <v>-1.5876</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4433</v>
+        <v>-0.7779</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0797</v>
+        <v>-0.8097</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1255</v>
+        <v>1.5627</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7053</v>
+        <v>-0.2806</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3177</v>
+        <v>-0.0645</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3876</v>
+        <v>-0.2161</v>
       </c>
       <c r="V3" t="n">
-        <v>3.988</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3.3238</v>
+        <v>1.2186</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6642</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.099</v>
+        <v>2.1712</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8431</v>
+        <v>2.6</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9421</v>
+        <v>-0.4288</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.2949</v>
+        <v>2.2806</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.4157</v>
+        <v>1.175</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1208</v>
+        <v>1.1056</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.4097</v>
+        <v>3.5887</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.5311</v>
+        <v>2.2128</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1214</v>
+        <v>1.3758</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1148</v>
+        <v>-1.3081</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1154</v>
+        <v>-1.0379</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.2702</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9534</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9534</v>
+        <v>2.5395</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1102</v>
+        <v>-1.0372</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.652</v>
+        <v>-0.773</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5417999999999999</v>
+        <v>-0.2642</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5507</v>
+        <v>1.3186</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2186</v>
+        <v>2.7145</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3321</v>
+        <v>-1.3959</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8444</v>
+        <v>1.6554</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6</v>
+        <v>-0.742</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7556</v>
+        <v>2.3974</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2806</v>
+        <v>-1.2949</v>
       </c>
       <c r="H5" t="n">
-        <v>1.175</v>
+        <v>-1.4157</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1056</v>
+        <v>0.1208</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5887</v>
+        <v>-1.4097</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2128</v>
+        <v>-1.5311</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3758</v>
+        <v>0.1214</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3081</v>
+        <v>0.1148</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0379</v>
+        <v>0.1154</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2702</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5395</v>
+        <v>1.9534</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3641</v>
+        <v>-0.5538</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.773</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.591</v>
+        <v>-0.0029</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3186</v>
+        <v>1.5507</v>
       </c>
       <c r="W5" t="n">
-        <v>2.7145</v>
+        <v>1.2186</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3959</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3101</v>
+        <v>0.904</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8247</v>
+        <v>1.1232</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1348</v>
+        <v>-0.2192</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1507</v>
+        <v>-0.3343</v>
       </c>
       <c r="H6" t="n">
-        <v>1.825</v>
+        <v>-0.6851</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6743</v>
+        <v>0.3508</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4268</v>
+        <v>0.7641</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9657</v>
+        <v>0.1433</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5389</v>
+        <v>0.6208</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7239</v>
+        <v>-1.0984</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8593</v>
+        <v>-0.8283</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1354</v>
+        <v>-0.27</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S6" t="n">
-        <v>0.378</v>
+        <v>-0.4244</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.22</v>
+        <v>0.0819</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5979</v>
+        <v>-0.5063</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6093</v>
+        <v>0.0999</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0549</v>
+        <v>0.2772</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5545</v>
+        <v>-0.1773</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2297</v>
+        <v>0.8688</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2628</v>
+        <v>-0.9664</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0331</v>
+        <v>1.8352</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7753</v>
+        <v>1.1507</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4792</v>
+        <v>1.825</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2544</v>
+        <v>-0.6743</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2544</v>
+        <v>0.4268</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.9657</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2544</v>
+        <v>-0.5389</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4792</v>
+        <v>0.7239</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4792</v>
+        <v>0.8593</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.1354</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8683999999999999</v>
+        <v>-0.0633</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9851</v>
+        <v>-0.3617</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1167</v>
+        <v>0.2983</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6093</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.0549</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6093</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3984</v>
+        <v>0.7514</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6176</v>
+        <v>0.7572</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2192</v>
+        <v>-0.0058</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3343</v>
+        <v>0.7753</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6851</v>
+        <v>-0.4792</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3508</v>
+        <v>1.2544</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7641</v>
+        <v>1.2544</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1433</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6208</v>
+        <v>1.2544</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0984</v>
+        <v>-0.4792</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8283</v>
+        <v>-0.4792</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q8" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.4795</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.08939999999999999</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="W8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.5627</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.4237</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.5063</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.0999</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.2772</v>
-      </c>
       <c r="X8" t="n">
-        <v>-0.1773</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1864</v>
+        <v>0.492</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8753</v>
+        <v>1.193</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6889</v>
+        <v>-0.701</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8427</v>
+        <v>2.087</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3034</v>
+        <v>2.1006</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5393</v>
+        <v>-0.0136</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6332</v>
+        <v>3.48</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0409</v>
+        <v>2.6836</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6741</v>
+        <v>0.7965</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2095</v>
+        <v>-1.3931</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3443</v>
+        <v>-0.583</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1348</v>
+        <v>-0.8101</v>
       </c>
       <c r="P9" t="n">
-        <v>0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>0.586</v>
+        <v>2.5395</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4166</v>
+        <v>-1.3042</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2421</v>
+        <v>-0.8527</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1745</v>
+        <v>-0.4514</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4869</v>
+        <v>0.0999</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4869</v>
+        <v>-1.3959</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3542</v>
+        <v>-0.2953</v>
       </c>
       <c r="E10" t="n">
-        <v>0.728</v>
+        <v>-0.8753</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0823</v>
+        <v>0.58</v>
       </c>
       <c r="G10" t="n">
-        <v>2.087</v>
+        <v>-0.8427</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1006</v>
+        <v>-0.3034</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0136</v>
+        <v>-0.5393</v>
       </c>
       <c r="J10" t="n">
-        <v>3.48</v>
+        <v>-0.6332</v>
       </c>
       <c r="K10" t="n">
-        <v>2.6836</v>
+        <v>0.0409</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7965</v>
+        <v>-0.6741</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3931</v>
+        <v>-0.2095</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.583</v>
+        <v>-0.3443</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8101</v>
+        <v>0.1348</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5395</v>
+        <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1504</v>
+        <v>-0.5255</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3177</v>
+        <v>-0.2421</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8327</v>
+        <v>-0.2834</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0999</v>
+        <v>0.4869</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.3959</v>
+        <v>0.4869</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0263</v>
+        <v>-4.1481</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4213</v>
+        <v>-1.2708</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6049</v>
+        <v>-2.8773</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2439</v>
@@ -1312,13 +1312,13 @@
         <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5903</v>
+        <v>0.4684</v>
       </c>
       <c r="T11" t="n">
-        <v>1.175</v>
+        <v>0.3255</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4153</v>
+        <v>0.143</v>
       </c>
       <c r="V11" t="n">
         <v>-2.6146</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.664099999999998</v>
+        <v>8.966799999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>7.473599999999999</v>
+        <v>7.776200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.190499999999999</v>
+        <v>1.1906</v>
       </c>
       <c r="G12" t="n">
-        <v>4.3483</v>
+        <v>4.348300000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9745999999999999</v>
+        <v>0.9745999999999998</v>
       </c>
       <c r="I12" t="n">
         <v>3.373399999999999</v>
@@ -1372,13 +1372,13 @@
         <v>7.423900000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.337899999999999</v>
+        <v>-8.337900000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.287400000000001</v>
+        <v>-4.2874</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.0504</v>
+        <v>-4.050400000000001</v>
       </c>
       <c r="P12" t="n">
         <v>4.8834</v>
@@ -1390,22 +1390,22 @@
         <v>17.5809</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.2784</v>
+        <v>-3.9757</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.708900000000001</v>
+        <v>-2.4063</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5695</v>
+        <v>-1.5693</v>
       </c>
       <c r="V12" t="n">
-        <v>3.7108</v>
+        <v>3.710800000000001</v>
       </c>
       <c r="W12" t="n">
         <v>10.1937</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.482899999999999</v>
+        <v>-6.4829</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8978</v>
+        <v>5.636</v>
       </c>
       <c r="E13" t="n">
-        <v>5.5586</v>
+        <v>5.053</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3393</v>
+        <v>0.583</v>
       </c>
       <c r="G13" t="n">
         <v>4.5589</v>
@@ -1468,13 +1468,13 @@
         <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8348</v>
+        <v>0.573</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3331</v>
+        <v>-0.1725</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5017</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2772</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.9171</v>
+        <v>3.3639</v>
       </c>
       <c r="E14" t="n">
-        <v>5.287</v>
+        <v>3.8714</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.37</v>
+        <v>-0.5075</v>
       </c>
       <c r="G14" t="n">
         <v>-1.0933</v>
@@ -1546,13 +1546,13 @@
         <v>2.1488</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5713</v>
+        <v>2.0181</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2481</v>
+        <v>0.8325</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3232</v>
+        <v>1.1856</v>
       </c>
       <c r="V14" t="n">
         <v>1.4624</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.0311</v>
+        <v>-0.821</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8104</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2207</v>
+        <v>-0.1118</v>
       </c>
       <c r="G15" t="n">
         <v>0.338</v>
@@ -1624,13 +1624,13 @@
         <v>0.3907</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.783</v>
+        <v>-0.573</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1816</v>
+        <v>-0.0805</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6015</v>
+        <v>-0.4925</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.0744</v>
+        <v>-1.6168</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.5679</v>
+        <v>-2.1635</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4935</v>
+        <v>0.5466</v>
       </c>
       <c r="G16" t="n">
         <v>-2.4239</v>
@@ -1702,13 +1702,13 @@
         <v>2.3441</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1876</v>
+        <v>0.6452</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5226</v>
+        <v>-0.1181</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.7633</v>
       </c>
       <c r="V16" t="n">
         <v>-0.0335</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.1485</v>
+        <v>-1.6345</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.2405</v>
+        <v>-0.4219</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0919</v>
+        <v>-1.2125</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.6485</v>
+        <v>1.0353</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1914</v>
+        <v>1.4676</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.4572</v>
+        <v>-0.4323</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.754</v>
+        <v>3.6325</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.9159</v>
+        <v>2.1757</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1619</v>
+        <v>1.4568</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8945</v>
+        <v>-2.5971</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7245</v>
+        <v>-0.7081</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.619</v>
+        <v>-1.8891</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1721</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9301</v>
+        <v>-4.8836</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>2.3441</v>
       </c>
       <c r="S17" t="n">
-        <v>0.34</v>
+        <v>0.2566</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8335</v>
+        <v>-0.2798</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1735</v>
+        <v>0.5364</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3321</v>
+        <v>-0.3869</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>1.1089</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0549</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3994</v>
+        <v>-1.7532</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-3.7349</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6742</v>
+        <v>1.9816</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0353</v>
+        <v>-1.6485</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4676</v>
+        <v>-0.1914</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4323</v>
+        <v>-1.4572</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6325</v>
+        <v>-0.754</v>
       </c>
       <c r="K18" t="n">
-        <v>2.1757</v>
+        <v>-0.9159</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4568</v>
+        <v>0.1619</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5971</v>
+        <v>-0.8945</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7081</v>
+        <v>0.7245</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.8891</v>
+        <v>-1.619</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.5395</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.8836</v>
+        <v>-2.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3441</v>
+        <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5084</v>
+        <v>0.7352</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5831</v>
+        <v>-0.328</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0747</v>
+        <v>1.0632</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3869</v>
+        <v>0.3321</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1089</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4959</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4968</v>
+        <v>-2.0457</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3274</v>
+        <v>-1.8219</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1693</v>
+        <v>-0.2238</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9379999999999999</v>
@@ -1936,13 +1936,13 @@
         <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1849</v>
+        <v>0.2662</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3494</v>
+        <v>0.1562</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1645</v>
+        <v>0.11</v>
       </c>
       <c r="V19" t="n">
         <v>0.1889</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6711</v>
+        <v>-2.4255</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2445</v>
+        <v>-2.0558</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9155</v>
+        <v>-0.3697</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.69</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.7703</v>
+        <v>0.065</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0803</v>
+        <v>-0.135</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7776</v>
+        <v>-0.2648</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.8586</v>
+        <v>0.4093</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0809</v>
+        <v>-0.6741</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9123</v>
+        <v>0.1948</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.9118</v>
+        <v>-0.3443</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.5391</v>
       </c>
       <c r="P20" t="n">
-        <v>0.586</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1953</v>
+        <v>-2.1488</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7985</v>
+        <v>0.0454</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9988</v>
+        <v>0.3577</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2004</v>
+        <v>-0.3123</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3656</v>
+        <v>-0.6428</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.5842</v>
+        <v>-0.6428</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9662</v>
+        <v>-2.9199</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4603</v>
+        <v>-0.0589</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5059</v>
+        <v>-2.8611</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-3.69</v>
       </c>
       <c r="H21" t="n">
-        <v>0.065</v>
+        <v>-3.7703</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.135</v>
+        <v>0.0803</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2648</v>
+        <v>-1.7776</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4093</v>
+        <v>-1.8586</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6741</v>
+        <v>0.0809</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1948</v>
+        <v>-1.9123</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3443</v>
+        <v>-1.9118</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5391</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4952</v>
+        <v>0.5496</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0467</v>
+        <v>0.6955</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4485</v>
+        <v>-0.1459</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6428</v>
+        <v>-0.3656</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6428</v>
+        <v>-1.5842</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6916</v>
+        <v>-3.7733</v>
       </c>
       <c r="E22" t="n">
         <v>0.8512</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.5428</v>
+        <v>-4.6245</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4167</v>
@@ -2170,13 +2170,13 @@
         <v>0.1953</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5178</v>
+        <v>0.4361</v>
       </c>
       <c r="T22" t="n">
         <v>0.5063</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0115</v>
+        <v>-0.0702</v>
       </c>
       <c r="V22" t="n">
         <v>-3.988</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.664200000000001</v>
+        <v>-7.99</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.190499999999999</v>
+        <v>-1.190500000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.473700000000001</v>
+        <v>-6.7997</v>
       </c>
       <c r="G23" t="n">
         <v>-4.348199999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9749000000000003</v>
+        <v>-0.9749000000000001</v>
       </c>
       <c r="I23" t="n">
         <v>-3.373600000000001</v>
@@ -2227,7 +2227,7 @@
         <v>4.2871</v>
       </c>
       <c r="L23" t="n">
-        <v>4.050599999999999</v>
+        <v>4.0506</v>
       </c>
       <c r="M23" t="n">
         <v>-12.6859</v>
@@ -2248,13 +2248,13 @@
         <v>12.6973</v>
       </c>
       <c r="S23" t="n">
-        <v>4.2785</v>
+        <v>4.9524</v>
       </c>
       <c r="T23" t="n">
-        <v>1.5694</v>
+        <v>1.5693</v>
       </c>
       <c r="U23" t="n">
-        <v>2.7089</v>
+        <v>3.3831</v>
       </c>
       <c r="V23" t="n">
         <v>-3.7106</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484292_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484292_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2398</v>
+        <v>2.1712</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6994</v>
+        <v>2.6</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4596</v>
+        <v>-0.4288</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9344</v>
+        <v>2.2806</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0202</v>
+        <v>1.175</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9141</v>
+        <v>1.1056</v>
       </c>
       <c r="J3" t="n">
-        <v>4.522</v>
+        <v>3.5887</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7982</v>
+        <v>2.2128</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7238</v>
+        <v>1.3758</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5876</v>
+        <v>-1.3081</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7779</v>
+        <v>-1.0379</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8097</v>
+        <v>-0.2702</v>
       </c>
       <c r="P3" t="n">
-        <v>0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5627</v>
+        <v>2.5395</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2806</v>
+        <v>-1.0372</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0645</v>
+        <v>-0.773</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2161</v>
+        <v>-0.2642</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.3186</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2186</v>
+        <v>2.7145</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2186</v>
+        <v>-1.3959</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +736,72 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1712</v>
+        <v>1.8279</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6</v>
+        <v>1.8279</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4288</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2806</v>
+        <v>1.8279</v>
       </c>
       <c r="H4" t="n">
-        <v>1.175</v>
+        <v>0.614</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1056</v>
+        <v>1.214</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5887</v>
+        <v>1.8279</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2128</v>
+        <v>0.614</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3758</v>
+        <v>1.214</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3081</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0379</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2702</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0372</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.773</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2642</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3186</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.3959</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.904</v>
+        <v>1.4119</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1232</v>
+        <v>2.8715</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2192</v>
+        <v>-1.4596</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3343</v>
+        <v>1.1064</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6851</v>
+        <v>-0.5937</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3508</v>
+        <v>1.7002</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7641</v>
+        <v>2.6941</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1433</v>
+        <v>0.1842</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6208</v>
+        <v>2.5099</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0984</v>
+        <v>-1.5876</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8283</v>
+        <v>-0.7779</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.27</v>
+        <v>-0.8097</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
         <v>1.5627</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4244</v>
+        <v>-0.2806</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0819</v>
+        <v>-0.0645</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5063</v>
+        <v>-0.2161</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0999</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1773</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8688</v>
+        <v>0.904</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9664</v>
+        <v>1.1232</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8352</v>
+        <v>-0.2192</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1507</v>
+        <v>-0.3343</v>
       </c>
       <c r="H7" t="n">
-        <v>1.825</v>
+        <v>-0.6851</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6743</v>
+        <v>0.3508</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4268</v>
+        <v>0.7641</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9657</v>
+        <v>0.1433</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5389</v>
+        <v>0.6208</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7239</v>
+        <v>-1.0984</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8593</v>
+        <v>-0.8283</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1354</v>
+        <v>-0.27</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0633</v>
+        <v>-0.4244</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3617</v>
+        <v>0.0819</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2983</v>
+        <v>-0.5063</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6093</v>
+        <v>0.0999</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0549</v>
+        <v>0.2772</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5545</v>
+        <v>-0.1773</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7514</v>
+        <v>0.8688</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7572</v>
+        <v>-0.9664</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0058</v>
+        <v>1.8352</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7753</v>
+        <v>1.1507</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4792</v>
+        <v>1.825</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2544</v>
+        <v>-0.6743</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2544</v>
+        <v>0.4268</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.9657</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2544</v>
+        <v>-0.5389</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4792</v>
+        <v>0.7239</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4792</v>
+        <v>0.8593</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.1354</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3901</v>
+        <v>-0.0633</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4795</v>
+        <v>-0.3617</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.08939999999999999</v>
+        <v>0.2983</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6093</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.0549</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6093</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.492</v>
+        <v>0.7514</v>
       </c>
       <c r="E9" t="n">
-        <v>1.193</v>
+        <v>0.7572</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.701</v>
+        <v>-0.0058</v>
       </c>
       <c r="G9" t="n">
-        <v>2.087</v>
+        <v>0.7753</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1006</v>
+        <v>-0.4792</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0136</v>
+        <v>1.2544</v>
       </c>
       <c r="J9" t="n">
-        <v>3.48</v>
+        <v>1.2544</v>
       </c>
       <c r="K9" t="n">
-        <v>2.6836</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7965</v>
+        <v>1.2544</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3931</v>
+        <v>-0.4792</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.583</v>
+        <v>-0.4792</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8101</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5395</v>
+        <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3042</v>
+        <v>0.3901</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8527</v>
+        <v>0.4795</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4514</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0999</v>
+        <v>-0.6093</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3959</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2953</v>
+        <v>0.492</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8753</v>
+        <v>1.193</v>
       </c>
       <c r="F10" t="n">
-        <v>0.58</v>
+        <v>-0.701</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8427</v>
+        <v>2.087</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3034</v>
+        <v>2.1006</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5393</v>
+        <v>-0.0136</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6332</v>
+        <v>3.48</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0409</v>
+        <v>2.6836</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6741</v>
+        <v>0.7965</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2095</v>
+        <v>-1.3931</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3443</v>
+        <v>-0.583</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1348</v>
+        <v>-0.8101</v>
       </c>
       <c r="P10" t="n">
-        <v>0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>0.586</v>
+        <v>2.5395</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5255</v>
+        <v>-1.3042</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2421</v>
+        <v>-0.8527</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2834</v>
+        <v>-0.4514</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4869</v>
+        <v>0.0999</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4869</v>
+        <v>-1.3959</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1481</v>
+        <v>-0.2953</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2708</v>
+        <v>-0.8753</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8773</v>
+        <v>0.58</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2439</v>
+        <v>-0.8427</v>
       </c>
       <c r="H11" t="n">
-        <v>1.671</v>
+        <v>-0.3034</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9149</v>
+        <v>-0.5393</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3338</v>
+        <v>-0.6332</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4392</v>
+        <v>0.0409</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1054</v>
+        <v>-0.6741</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5777</v>
+        <v>-0.2095</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7682</v>
+        <v>-0.3443</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8095</v>
+        <v>0.1348</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4684</v>
+        <v>-0.5255</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3255</v>
+        <v>-0.2421</v>
       </c>
       <c r="U11" t="n">
-        <v>0.143</v>
+        <v>-0.2834</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.6146</v>
+        <v>0.4869</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.6146</v>
+        <v>0.4869</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,151 +1400,157 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.966799999999999</v>
+        <v>-4.1481</v>
       </c>
       <c r="E12" t="n">
-        <v>7.776200000000001</v>
+        <v>-1.2708</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1906</v>
+        <v>-2.8773</v>
       </c>
       <c r="G12" t="n">
-        <v>4.348300000000001</v>
+        <v>-0.2439</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9745999999999998</v>
+        <v>1.671</v>
       </c>
       <c r="I12" t="n">
-        <v>3.373399999999999</v>
+        <v>-1.9149</v>
       </c>
       <c r="J12" t="n">
-        <v>12.686</v>
+        <v>1.3338</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2621</v>
+        <v>2.4392</v>
       </c>
       <c r="L12" t="n">
-        <v>7.423900000000001</v>
+        <v>-1.1054</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.337900000000001</v>
+        <v>-1.5777</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.2874</v>
+        <v>-0.7682</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.050400000000001</v>
+        <v>-0.8095</v>
       </c>
       <c r="P12" t="n">
-        <v>4.8834</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.6971</v>
+        <v>-2.9301</v>
       </c>
       <c r="R12" t="n">
-        <v>17.5809</v>
+        <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.9757</v>
+        <v>0.4684</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.4063</v>
+        <v>0.3255</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5693</v>
+        <v>0.143</v>
       </c>
       <c r="V12" t="n">
-        <v>3.710800000000001</v>
+        <v>-2.6146</v>
       </c>
       <c r="W12" t="n">
-        <v>10.1937</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.4829</v>
+        <v>-2.6146</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N. DEL VAL GARCIA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+          <t>TQ-CB PRAT</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.636</v>
+        <v>8.966799999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>5.053</v>
+        <v>7.776199999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.583</v>
+        <v>1.1906</v>
       </c>
       <c r="G13" t="n">
-        <v>4.5589</v>
+        <v>4.348200000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4733</v>
+        <v>0.9747</v>
       </c>
       <c r="I13" t="n">
-        <v>5.0322</v>
+        <v>3.3735</v>
       </c>
       <c r="J13" t="n">
-        <v>6.2022</v>
+        <v>12.686</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.449</v>
+        <v>5.2621</v>
       </c>
       <c r="L13" t="n">
-        <v>6.6512</v>
+        <v>7.424000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6433</v>
+        <v>-8.337900000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0243</v>
+        <v>-4.2874</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.619</v>
+        <v>-4.050400000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7814</v>
+        <v>4.8834</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>-12.6971</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7581</v>
+        <v>17.5809</v>
       </c>
       <c r="S13" t="n">
-        <v>0.573</v>
+        <v>-3.9757</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1725</v>
+        <v>-2.4063</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7455000000000001</v>
+        <v>-1.5693</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2772</v>
+        <v>3.7108</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>10.1937</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2772</v>
-      </c>
+        <v>-6.4829</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. SIMON</t>
+          <t>N. DEL VAL GARCIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3639</v>
+        <v>5.636</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8714</v>
+        <v>5.053</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5075</v>
+        <v>0.583</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.0933</v>
+        <v>4.5589</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7549</v>
+        <v>-0.4733</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.8482</v>
+        <v>5.0322</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1644</v>
+        <v>6.2022</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9887</v>
+        <v>-0.449</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1757</v>
+        <v>6.6512</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.2577</v>
+        <v>-1.6433</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2338</v>
+        <v>-0.0243</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.0239</v>
+        <v>-1.619</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0181</v>
+        <v>0.573</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8325</v>
+        <v>-0.1725</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1856</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4624</v>
+        <v>-0.2772</v>
       </c>
       <c r="W14" t="n">
-        <v>3.0466</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.5842</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>A. SIMON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.821</v>
+        <v>3.3639</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7092000000000001</v>
+        <v>3.8714</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1118</v>
+        <v>-0.5075</v>
       </c>
       <c r="G15" t="n">
-        <v>0.338</v>
+        <v>-1.0933</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3359</v>
+        <v>0.7549</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6739000000000001</v>
+        <v>-1.8482</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3479</v>
+        <v>1.1644</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3479</v>
+        <v>0.9887</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.1757</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-2.2577</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6838</v>
+        <v>-0.2338</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6739000000000001</v>
+        <v>-2.0239</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3907</v>
+        <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.573</v>
+        <v>2.0181</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0805</v>
+        <v>0.8325</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4925</v>
+        <v>1.1856</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.4624</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.0466</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.5842</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.6168</v>
+        <v>-0.821</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.1635</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5466</v>
+        <v>-0.1118</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.4239</v>
+        <v>0.338</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0558</v>
+        <v>-0.3359</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.4797</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5059</v>
+        <v>0.3479</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3545</v>
+        <v>0.3479</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.8604</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.918</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2988</v>
+        <v>-0.6838</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6192</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3441</v>
+        <v>0.3907</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6452</v>
+        <v>-0.573</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1181</v>
+        <v>-0.0805</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7633</v>
+        <v>-0.4925</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.0335</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6428</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6345</v>
+        <v>-1.6168</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4219</v>
+        <v>-2.1635</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2125</v>
+        <v>0.5466</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0353</v>
+        <v>-2.4239</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4676</v>
+        <v>1.0558</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4323</v>
+        <v>-3.4797</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6325</v>
+        <v>-0.5059</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1757</v>
+        <v>1.3545</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4568</v>
+        <v>-1.8604</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5971</v>
+        <v>-1.918</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7081</v>
+        <v>-0.2988</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8891</v>
+        <v>-1.6192</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.5395</v>
+        <v>0.1953</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.8836</v>
+        <v>-2.1488</v>
       </c>
       <c r="R17" t="n">
         <v>2.3441</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2566</v>
+        <v>0.6452</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2798</v>
+        <v>-0.1181</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5364</v>
+        <v>0.7633</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3869</v>
+        <v>-0.0335</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1089</v>
+        <v>0.6093</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4959</v>
+        <v>-0.6428</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7532</v>
+        <v>-1.6345</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.7349</v>
+        <v>-0.4219</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9816</v>
+        <v>-1.2125</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.6485</v>
+        <v>1.0353</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1914</v>
+        <v>1.4676</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4572</v>
+        <v>-0.4323</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.754</v>
+        <v>3.6325</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9159</v>
+        <v>2.1757</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1619</v>
+        <v>1.4568</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8945</v>
+        <v>-2.5971</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7245</v>
+        <v>-0.7081</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.619</v>
+        <v>-1.8891</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1721</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9301</v>
+        <v>-4.8836</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>2.3441</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7352</v>
+        <v>0.2566</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.328</v>
+        <v>-0.2798</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0632</v>
+        <v>0.5364</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3321</v>
+        <v>-0.3869</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>1.1089</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0549</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. SIMS SERRA</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0457</v>
+        <v>-1.7532</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8219</v>
+        <v>-3.7349</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2238</v>
+        <v>1.9816</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9379999999999999</v>
+        <v>-1.6485</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8149999999999999</v>
+        <v>-0.1914</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7531</v>
+        <v>-1.4572</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3838</v>
+        <v>-0.754</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6385</v>
+        <v>-0.9159</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.0223</v>
+        <v>0.1619</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5542</v>
+        <v>-0.8945</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8235</v>
+        <v>0.7245</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2692</v>
+        <v>-1.619</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5627</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1488</v>
+        <v>-2.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2662</v>
+        <v>0.7352</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1562</v>
+        <v>-0.328</v>
       </c>
       <c r="U19" t="n">
-        <v>0.11</v>
+        <v>1.0632</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1889</v>
+        <v>0.3321</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5545</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3656</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>E. SIMS SERRA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4255</v>
+        <v>-2.0457</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0558</v>
+        <v>-1.8219</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3697</v>
+        <v>-0.2238</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.065</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.135</v>
+        <v>-1.7531</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2648</v>
+        <v>-0.3838</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4093</v>
+        <v>1.6385</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6741</v>
+        <v>-2.0223</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1948</v>
+        <v>-0.5542</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3443</v>
+        <v>-0.8235</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5391</v>
+        <v>0.2692</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7581</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.1488</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0454</v>
+        <v>0.2662</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3577</v>
+        <v>0.1562</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3123</v>
+        <v>0.11</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6428</v>
+        <v>0.1889</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6428</v>
+        <v>-0.3656</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9199</v>
+        <v>-2.4255</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0589</v>
+        <v>-2.0558</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8611</v>
+        <v>-0.3697</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.69</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.7703</v>
+        <v>0.065</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0803</v>
+        <v>-0.135</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7776</v>
+        <v>-0.2648</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.8586</v>
+        <v>0.4093</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0809</v>
+        <v>-0.6741</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9123</v>
+        <v>0.1948</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.9118</v>
+        <v>-0.3443</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.5391</v>
       </c>
       <c r="P21" t="n">
-        <v>0.586</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1953</v>
+        <v>-2.1488</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5496</v>
+        <v>0.0454</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6955</v>
+        <v>0.3577</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1459</v>
+        <v>-0.3123</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3656</v>
+        <v>-0.6428</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.5842</v>
+        <v>-0.6428</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7733</v>
+        <v>-2.9199</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8512</v>
+        <v>-0.0589</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.6245</v>
+        <v>-2.8611</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4167</v>
+        <v>-3.69</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3623</v>
+        <v>-3.7703</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0545</v>
+        <v>0.0803</v>
       </c>
       <c r="J22" t="n">
-        <v>0.677</v>
+        <v>-1.7776</v>
       </c>
       <c r="K22" t="n">
-        <v>0.596</v>
+        <v>-1.8586</v>
       </c>
       <c r="L22" t="n">
         <v>0.0809</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0937</v>
+        <v>-1.9123</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9583</v>
+        <v>-1.9118</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1354</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4361</v>
+        <v>0.5496</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5063</v>
+        <v>0.6955</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0702</v>
+        <v>-0.1459</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.988</v>
+        <v>-0.3656</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3321</v>
+        <v>1.2186</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.6559</v>
+        <v>-1.5842</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>O. SUBIRANAS CASELLAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,152 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>-3.7733</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.8512</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-4.6245</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.4167</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.3623</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.0545</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.0809</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.0937</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.9583</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.1354</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.4361</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.5063</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.0702</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-3.988</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-0.3321</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-3.6559</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484292_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
         <v>-7.99</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E24" t="n">
         <v>-1.190500000000001</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F24" t="n">
         <v>-6.7997</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G24" t="n">
         <v>-4.348199999999999</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H24" t="n">
         <v>-0.9749000000000001</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I24" t="n">
         <v>-3.373600000000001</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>8.337899999999999</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K24" t="n">
         <v>4.2871</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L24" t="n">
         <v>4.0506</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M24" t="n">
         <v>-12.6859</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N24" t="n">
         <v>-5.2622</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O24" t="n">
         <v>-7.423999999999999</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P24" t="n">
         <v>-4.8837</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q24" t="n">
         <v>-17.5809</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>12.6973</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S24" t="n">
         <v>4.9524</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>1.5693</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>3.3831</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V24" t="n">
         <v>-3.7106</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W24" t="n">
         <v>6.483</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X24" t="n">
         <v>-10.1937</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
